--- a/questions.xlsx
+++ b/questions.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kubonanako/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{232FBD1E-EB01-7C45-BA32-363E6B3163C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{AB9EE969-8E9A-8A41-858B-C80DEA7F46D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1400" yWindow="600" windowWidth="27400" windowHeight="16120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="12800" yWindow="600" windowWidth="14380" windowHeight="16120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="調査概要" sheetId="1" r:id="rId1"/>
@@ -19,11 +19,12 @@
     <sheet name="ロジック" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="0"/>
+  <fileRecoveryPr repairLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="84">
   <si>
     <t>項目</t>
   </si>
@@ -53,9 +54,6 @@
   </si>
   <si>
     <t>設問文</t>
-  </si>
-  <si>
-    <t>回答形式（単一選択 / 複数選択 / 自由記述 / 数値）</t>
   </si>
   <si>
     <t>選択肢（カンマ区切り）</t>
@@ -293,13 +291,7 @@
       <t>キョジュウ</t>
     </rPh>
     <rPh sb="8" eb="10">
-      <t>センタク</t>
-    </rPh>
-    <rPh sb="17" eb="19">
-      <t>タンイ</t>
-    </rPh>
-    <rPh sb="19" eb="21">
-      <t>センタク</t>
+      <t>センタクタンイセンタク</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -354,34 +346,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>0回（3年以上前に訪問した）,1〜2回,3〜4回,5〜6回,6回以上</t>
-    <rPh sb="1" eb="2">
-      <t>カイ</t>
-    </rPh>
-    <rPh sb="4" eb="5">
-      <t>ネn</t>
-    </rPh>
-    <rPh sb="5" eb="8">
-      <t>ネn</t>
-    </rPh>
-    <rPh sb="9" eb="11">
-      <t>ホウモn</t>
-    </rPh>
-    <rPh sb="18" eb="19">
-      <t>カイ</t>
-    </rPh>
-    <rPh sb="23" eb="24">
-      <t>カイ</t>
-    </rPh>
-    <rPh sb="28" eb="29">
-      <t>カイ</t>
-    </rPh>
-    <rPh sb="31" eb="34">
-      <t>カイイジヨ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>複数選択</t>
     <rPh sb="0" eb="2">
       <t>フクスウ</t>
@@ -426,6 +390,175 @@
   </si>
   <si>
     <t>Q8</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Q8</t>
+  </si>
+  <si>
+    <t>Q9</t>
+  </si>
+  <si>
+    <t>Q10</t>
+  </si>
+  <si>
+    <t>Q11</t>
+  </si>
+  <si>
+    <t>Q12</t>
+  </si>
+  <si>
+    <t>Q13</t>
+  </si>
+  <si>
+    <t>Q14</t>
+  </si>
+  <si>
+    <t>Q15</t>
+  </si>
+  <si>
+    <t>Q16</t>
+  </si>
+  <si>
+    <t>〇〇地域の食品や飲料を購入したことがありますか？（購入場所はどこでも可）</t>
+    <rPh sb="2" eb="4">
+      <t>チイキ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ショク</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>インリョウ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>コウニュウ</t>
+    </rPh>
+    <rPh sb="25" eb="29">
+      <t>コウニュウ</t>
+    </rPh>
+    <rPh sb="34" eb="35">
+      <t xml:space="preserve">カ </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>はい→Q9 / いいえ→END</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ここ3年で〇〇地域の食品や飲料を購入した回数を選択肢してください。</t>
+    <rPh sb="3" eb="4">
+      <t>ネn</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>チイ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ショクヒn</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>インリョウ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>コウニュウ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>カイスウ</t>
+    </rPh>
+    <rPh sb="23" eb="26">
+      <t>センタク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>0回（3年以上前に訪問した）,1〜2回,3〜4回,5〜6回,7回以上</t>
+    <rPh sb="1" eb="2">
+      <t>カイ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ネn</t>
+    </rPh>
+    <rPh sb="5" eb="8">
+      <t>ネn</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ホウモn</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>カイ</t>
+    </rPh>
+    <rPh sb="23" eb="24">
+      <t>カイ</t>
+    </rPh>
+    <rPh sb="28" eb="29">
+      <t>カイ</t>
+    </rPh>
+    <rPh sb="31" eb="34">
+      <t>カイイジヨ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Q10</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>0回（3年以上前に購入した）,1〜2回,3〜4回,5〜6回,7回以上</t>
+    <rPh sb="1" eb="2">
+      <t>カイ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>カイ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>コウニュウ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>カイ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>カイ</t>
+    </rPh>
+    <rPh sb="19" eb="20">
+      <t>カイ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>イジョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>〇〇地域と聞いて、思いつくものを5つ以内で回答してください。正解はありません。</t>
+    <rPh sb="2" eb="4">
+      <t>チイキ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>キイ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>オモイ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>イナイ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>カイトウ</t>
+    </rPh>
+    <rPh sb="30" eb="32">
+      <t>セイカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>回答形式（単一選択 / 複数選択 / 自由記述 / 数値）</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>text5</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Q11</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -796,7 +929,7 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -804,7 +937,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -812,7 +945,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -820,7 +953,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -834,7 +967,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -842,7 +975,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -850,7 +983,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
   </sheetData>
@@ -861,11 +994,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:H17"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="15.33203125" customWidth="1"/>
-    <col min="2" max="2" width="60.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="78.5" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="28" customWidth="1"/>
     <col min="4" max="4" width="58.5" bestFit="1" customWidth="1"/>
     <col min="5" max="8" width="28" customWidth="1"/>
@@ -879,162 +1012,249 @@
         <v>9</v>
       </c>
       <c r="C1" t="s">
+        <v>81</v>
+      </c>
+      <c r="D1" t="s">
         <v>10</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>11</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>12</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>13</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>14</v>
-      </c>
-      <c r="H1" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2" t="s">
+        <v>48</v>
+      </c>
+      <c r="D2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E2" t="s">
         <v>16</v>
       </c>
-      <c r="B2" t="s">
-        <v>47</v>
-      </c>
-      <c r="C2" t="s">
-        <v>49</v>
-      </c>
-      <c r="D2" t="s">
-        <v>50</v>
-      </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>17</v>
-      </c>
-      <c r="F2" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C3" t="s">
+        <v>48</v>
+      </c>
+      <c r="D3" t="s">
+        <v>51</v>
+      </c>
+      <c r="E3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F3" t="s">
         <v>18</v>
-      </c>
-      <c r="B3" t="s">
-        <v>51</v>
-      </c>
-      <c r="C3" t="s">
-        <v>49</v>
-      </c>
-      <c r="D3" t="s">
-        <v>52</v>
-      </c>
-      <c r="E3" t="s">
-        <v>17</v>
-      </c>
-      <c r="F3" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" t="s">
+        <v>53</v>
+      </c>
+      <c r="C4" t="s">
+        <v>47</v>
+      </c>
+      <c r="D4" t="s">
+        <v>52</v>
+      </c>
+      <c r="E4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F4" t="s">
         <v>19</v>
-      </c>
-      <c r="B4" t="s">
-        <v>54</v>
-      </c>
-      <c r="C4" t="s">
-        <v>48</v>
-      </c>
-      <c r="D4" t="s">
-        <v>53</v>
-      </c>
-      <c r="E4" t="s">
-        <v>17</v>
-      </c>
-      <c r="F4" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B5" t="s">
+        <v>55</v>
+      </c>
+      <c r="C5" t="s">
+        <v>47</v>
+      </c>
+      <c r="D5" t="s">
+        <v>54</v>
+      </c>
+      <c r="E5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G5" t="s">
         <v>56</v>
-      </c>
-      <c r="C5" t="s">
-        <v>48</v>
-      </c>
-      <c r="D5" t="s">
-        <v>55</v>
-      </c>
-      <c r="E5" t="s">
-        <v>17</v>
-      </c>
-      <c r="G5" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B6" t="s">
+        <v>57</v>
+      </c>
+      <c r="C6" t="s">
+        <v>47</v>
+      </c>
+      <c r="D6" t="s">
+        <v>54</v>
+      </c>
+      <c r="E6" t="s">
+        <v>16</v>
+      </c>
+      <c r="G6" t="s">
         <v>58</v>
-      </c>
-      <c r="C6" t="s">
-        <v>48</v>
-      </c>
-      <c r="D6" t="s">
-        <v>55</v>
-      </c>
-      <c r="E6" t="s">
-        <v>17</v>
-      </c>
-      <c r="G6" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C7" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D7" t="s">
-        <v>61</v>
+        <v>77</v>
       </c>
       <c r="E7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F7" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="8" spans="1:8">
       <c r="A8" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B8" t="s">
+        <v>62</v>
+      </c>
+      <c r="C8" t="s">
+        <v>60</v>
+      </c>
+      <c r="D8" t="s">
+        <v>61</v>
+      </c>
+      <c r="E8" t="s">
+        <v>16</v>
+      </c>
+      <c r="F8" t="s">
         <v>64</v>
       </c>
-      <c r="C8" t="s">
-        <v>62</v>
-      </c>
-      <c r="D8" t="s">
-        <v>63</v>
-      </c>
-      <c r="E8" t="s">
-        <v>17</v>
-      </c>
-      <c r="F8" t="s">
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" t="s">
+        <v>65</v>
+      </c>
+      <c r="B9" t="s">
+        <v>74</v>
+      </c>
+      <c r="C9" t="s">
+        <v>47</v>
+      </c>
+      <c r="D9" t="s">
+        <v>54</v>
+      </c>
+      <c r="E9" t="s">
+        <v>16</v>
+      </c>
+      <c r="G9" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" t="s">
         <v>66</v>
+      </c>
+      <c r="B10" t="s">
+        <v>76</v>
+      </c>
+      <c r="C10" t="s">
+        <v>47</v>
+      </c>
+      <c r="D10" t="s">
+        <v>79</v>
+      </c>
+      <c r="E10" t="s">
+        <v>16</v>
+      </c>
+      <c r="F10" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
+      <c r="A11" t="s">
+        <v>67</v>
+      </c>
+      <c r="B11" t="s">
+        <v>80</v>
+      </c>
+      <c r="C11" t="s">
+        <v>82</v>
+      </c>
+      <c r="E11" t="s">
+        <v>16</v>
+      </c>
+      <c r="F11" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
+      <c r="A12" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
+      <c r="A13" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
+      <c r="A14" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8">
+      <c r="A15" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8">
+      <c r="A16" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" t="s">
+        <v>73</v>
       </c>
     </row>
   </sheetData>
@@ -1055,31 +1275,31 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B1" t="s">
         <v>21</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>22</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>23</v>
-      </c>
-      <c r="D1" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
   </sheetData>
@@ -1099,37 +1319,37 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B1" t="s">
         <v>28</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>29</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>30</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>31</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>32</v>
-      </c>
-      <c r="F1" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
   </sheetData>

--- a/questions.xlsx
+++ b/questions.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kubonanako/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{AB9EE969-8E9A-8A41-858B-C80DEA7F46D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:20001_{91C6E91A-F7C8-5948-B403-9D3CD3C4DC63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12800" yWindow="600" windowWidth="14380" windowHeight="16120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="調査概要" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="88">
   <si>
     <t>項目</t>
   </si>
@@ -559,6 +559,36 @@
   </si>
   <si>
     <t>Q11</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>繰り返し元QID</t>
+  </si>
+  <si>
+    <t>糸島の「{word}」からさらに連想されることを3つ以内で回答してください。正解はありません。</t>
+    <rPh sb="0" eb="2">
+      <t>イトシマ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>レンソウ</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>イナイ</t>
+    </rPh>
+    <rPh sb="29" eb="31">
+      <t>カイトウ</t>
+    </rPh>
+    <rPh sb="38" eb="40">
+      <t>セイカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>tezt3</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Q12</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -994,17 +1024,17 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:H17"/>
+  <dimension ref="A1:I17"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="15.33203125" customWidth="1"/>
     <col min="2" max="2" width="78.5" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="28" customWidth="1"/>
     <col min="4" max="4" width="58.5" bestFit="1" customWidth="1"/>
-    <col min="5" max="8" width="28" customWidth="1"/>
+    <col min="5" max="9" width="28" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:9">
       <c r="A1" t="s">
         <v>8</v>
       </c>
@@ -1021,16 +1051,19 @@
         <v>11</v>
       </c>
       <c r="F1" t="s">
+        <v>84</v>
+      </c>
+      <c r="G1" t="s">
         <v>12</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>13</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:8">
+    <row r="2" spans="1:9">
       <c r="A2" t="s">
         <v>15</v>
       </c>
@@ -1046,11 +1079,11 @@
       <c r="E2" t="s">
         <v>16</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:8">
+    <row r="3" spans="1:9">
       <c r="A3" t="s">
         <v>17</v>
       </c>
@@ -1066,11 +1099,11 @@
       <c r="E3" t="s">
         <v>16</v>
       </c>
-      <c r="F3" t="s">
+      <c r="G3" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="4" spans="1:8">
+    <row r="4" spans="1:9">
       <c r="A4" t="s">
         <v>18</v>
       </c>
@@ -1086,11 +1119,11 @@
       <c r="E4" t="s">
         <v>16</v>
       </c>
-      <c r="F4" t="s">
+      <c r="G4" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:8">
+    <row r="5" spans="1:9">
       <c r="A5" t="s">
         <v>19</v>
       </c>
@@ -1106,11 +1139,11 @@
       <c r="E5" t="s">
         <v>16</v>
       </c>
-      <c r="G5" t="s">
+      <c r="H5" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="6" spans="1:8">
+    <row r="6" spans="1:9">
       <c r="A6" t="s">
         <v>43</v>
       </c>
@@ -1126,11 +1159,11 @@
       <c r="E6" t="s">
         <v>16</v>
       </c>
-      <c r="G6" t="s">
+      <c r="H6" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="7" spans="1:8">
+    <row r="7" spans="1:9">
       <c r="A7" t="s">
         <v>44</v>
       </c>
@@ -1146,11 +1179,11 @@
       <c r="E7" t="s">
         <v>16</v>
       </c>
-      <c r="F7" t="s">
+      <c r="G7" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="8" spans="1:8">
+    <row r="8" spans="1:9">
       <c r="A8" t="s">
         <v>45</v>
       </c>
@@ -1166,11 +1199,11 @@
       <c r="E8" t="s">
         <v>16</v>
       </c>
-      <c r="F8" t="s">
+      <c r="G8" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="9" spans="1:8">
+    <row r="9" spans="1:9">
       <c r="A9" t="s">
         <v>65</v>
       </c>
@@ -1186,11 +1219,11 @@
       <c r="E9" t="s">
         <v>16</v>
       </c>
-      <c r="G9" t="s">
+      <c r="H9" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="10" spans="1:8">
+    <row r="10" spans="1:9">
       <c r="A10" t="s">
         <v>66</v>
       </c>
@@ -1206,11 +1239,11 @@
       <c r="E10" t="s">
         <v>16</v>
       </c>
-      <c r="F10" t="s">
+      <c r="G10" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="11" spans="1:8">
+    <row r="11" spans="1:9">
       <c r="A11" t="s">
         <v>67</v>
       </c>
@@ -1223,31 +1256,46 @@
       <c r="E11" t="s">
         <v>16</v>
       </c>
-      <c r="F11" t="s">
+      <c r="G11" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="12" spans="1:8">
+    <row r="12" spans="1:9">
       <c r="A12" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="13" spans="1:8">
+      <c r="B12" t="s">
+        <v>85</v>
+      </c>
+      <c r="C12" t="s">
+        <v>86</v>
+      </c>
+      <c r="E12" t="s">
+        <v>16</v>
+      </c>
+      <c r="F12" t="s">
+        <v>78</v>
+      </c>
+      <c r="G12" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9">
       <c r="A13" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="14" spans="1:8">
+    <row r="14" spans="1:9">
       <c r="A14" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="15" spans="1:8">
+    <row r="15" spans="1:9">
       <c r="A15" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="16" spans="1:8">
+    <row r="16" spans="1:9">
       <c r="A16" t="s">
         <v>72</v>
       </c>

--- a/questions.xlsx
+++ b/questions.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kubonanako/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:20001_{91C6E91A-F7C8-5948-B403-9D3CD3C4DC63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:20001_{E499B1F1-9332-CA4C-93A4-7D09F768643B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="87">
   <si>
     <t>項目</t>
   </si>
@@ -391,9 +391,6 @@
   <si>
     <t>Q8</t>
     <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>Q8</t>
   </si>
   <si>
     <t>Q9</t>
@@ -1042,7 +1039,7 @@
         <v>9</v>
       </c>
       <c r="C1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D1" t="s">
         <v>10</v>
@@ -1051,7 +1048,7 @@
         <v>11</v>
       </c>
       <c r="F1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G1" t="s">
         <v>12</v>
@@ -1174,7 +1171,7 @@
         <v>47</v>
       </c>
       <c r="D7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E7" t="s">
         <v>16</v>
@@ -1205,10 +1202,10 @@
     </row>
     <row r="9" spans="1:9">
       <c r="A9" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B9" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C9" t="s">
         <v>47</v>
@@ -1220,89 +1217,89 @@
         <v>16</v>
       </c>
       <c r="H9" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B10" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C10" t="s">
         <v>47</v>
       </c>
       <c r="D10" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E10" t="s">
         <v>16</v>
       </c>
       <c r="G10" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B11" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C11" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E11" t="s">
         <v>16</v>
       </c>
       <c r="G11" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B12" t="s">
+        <v>84</v>
+      </c>
+      <c r="C12" t="s">
         <v>85</v>
-      </c>
-      <c r="C12" t="s">
-        <v>86</v>
       </c>
       <c r="E12" t="s">
         <v>16</v>
       </c>
       <c r="F12" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G12" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="14" spans="1:9">
       <c r="A14" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="16" spans="1:9">
       <c r="A16" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
   </sheetData>

--- a/questions.xlsx
+++ b/questions.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kubonanako/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:20001_{E499B1F1-9332-CA4C-93A4-7D09F768643B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:20001_{4CF4116E-A1B3-074C-B39C-8B5770C902FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/questions.xlsx
+++ b/questions.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kubonanako/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:20001_{4CF4116E-A1B3-074C-B39C-8B5770C902FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:20001_{4939D687-B65A-D34E-8A13-FA8B4D1B0076}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="88">
   <si>
     <t>項目</t>
   </si>
@@ -69,9 +69,6 @@
   </si>
   <si>
     <t>備考</t>
-  </si>
-  <si>
-    <t>Q1</t>
   </si>
   <si>
     <t>YES</t>
@@ -586,6 +583,14 @@
   </si>
   <si>
     <t>Q12</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Q1</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Q2</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -956,7 +961,7 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -964,7 +969,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -972,7 +977,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -980,7 +985,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -994,7 +999,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -1002,7 +1007,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -1010,7 +1015,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
   </sheetData>
@@ -1039,7 +1044,7 @@
         <v>9</v>
       </c>
       <c r="C1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D1" t="s">
         <v>10</v>
@@ -1048,7 +1053,7 @@
         <v>11</v>
       </c>
       <c r="F1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G1" t="s">
         <v>12</v>
@@ -1062,244 +1067,244 @@
     </row>
     <row r="2" spans="1:9">
       <c r="A2" t="s">
+        <v>86</v>
+      </c>
+      <c r="B2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E2" t="s">
         <v>15</v>
       </c>
-      <c r="B2" t="s">
-        <v>46</v>
-      </c>
-      <c r="C2" t="s">
-        <v>48</v>
-      </c>
-      <c r="D2" t="s">
-        <v>49</v>
-      </c>
-      <c r="E2" t="s">
+      <c r="G2" t="s">
         <v>16</v>
-      </c>
-      <c r="G2" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" t="s">
+        <v>87</v>
+      </c>
+      <c r="B3" t="s">
+        <v>49</v>
+      </c>
+      <c r="C3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D3" t="s">
+        <v>50</v>
+      </c>
+      <c r="E3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G3" t="s">
         <v>17</v>
-      </c>
-      <c r="B3" t="s">
-        <v>50</v>
-      </c>
-      <c r="C3" t="s">
-        <v>48</v>
-      </c>
-      <c r="D3" t="s">
-        <v>51</v>
-      </c>
-      <c r="E3" t="s">
-        <v>16</v>
-      </c>
-      <c r="G3" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B4" t="s">
+        <v>52</v>
+      </c>
+      <c r="C4" t="s">
+        <v>46</v>
+      </c>
+      <c r="D4" t="s">
+        <v>51</v>
+      </c>
+      <c r="E4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G4" t="s">
         <v>18</v>
-      </c>
-      <c r="B4" t="s">
-        <v>53</v>
-      </c>
-      <c r="C4" t="s">
-        <v>47</v>
-      </c>
-      <c r="D4" t="s">
-        <v>52</v>
-      </c>
-      <c r="E4" t="s">
-        <v>16</v>
-      </c>
-      <c r="G4" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B5" t="s">
+        <v>54</v>
+      </c>
+      <c r="C5" t="s">
+        <v>46</v>
+      </c>
+      <c r="D5" t="s">
+        <v>53</v>
+      </c>
+      <c r="E5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H5" t="s">
         <v>55</v>
-      </c>
-      <c r="C5" t="s">
-        <v>47</v>
-      </c>
-      <c r="D5" t="s">
-        <v>54</v>
-      </c>
-      <c r="E5" t="s">
-        <v>16</v>
-      </c>
-      <c r="H5" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B6" t="s">
+        <v>56</v>
+      </c>
+      <c r="C6" t="s">
+        <v>46</v>
+      </c>
+      <c r="D6" t="s">
+        <v>53</v>
+      </c>
+      <c r="E6" t="s">
+        <v>15</v>
+      </c>
+      <c r="H6" t="s">
         <v>57</v>
-      </c>
-      <c r="C6" t="s">
-        <v>47</v>
-      </c>
-      <c r="D6" t="s">
-        <v>54</v>
-      </c>
-      <c r="E6" t="s">
-        <v>16</v>
-      </c>
-      <c r="H6" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B7" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C7" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D7" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G7" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B8" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C8" t="s">
+        <v>59</v>
+      </c>
+      <c r="D8" t="s">
         <v>60</v>
       </c>
-      <c r="D8" t="s">
-        <v>61</v>
-      </c>
       <c r="E8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G8" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C9" t="s">
+        <v>46</v>
+      </c>
+      <c r="D9" t="s">
+        <v>53</v>
+      </c>
+      <c r="E9" t="s">
+        <v>15</v>
+      </c>
+      <c r="H9" t="s">
         <v>73</v>
-      </c>
-      <c r="C9" t="s">
-        <v>47</v>
-      </c>
-      <c r="D9" t="s">
-        <v>54</v>
-      </c>
-      <c r="E9" t="s">
-        <v>16</v>
-      </c>
-      <c r="H9" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B10" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C10" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D10" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E10" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G10" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B11" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C11" t="s">
+        <v>80</v>
+      </c>
+      <c r="E11" t="s">
+        <v>15</v>
+      </c>
+      <c r="G11" t="s">
         <v>81</v>
-      </c>
-      <c r="E11" t="s">
-        <v>16</v>
-      </c>
-      <c r="G11" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B12" t="s">
+        <v>83</v>
+      </c>
+      <c r="C12" t="s">
         <v>84</v>
       </c>
-      <c r="C12" t="s">
+      <c r="E12" t="s">
+        <v>15</v>
+      </c>
+      <c r="F12" t="s">
+        <v>76</v>
+      </c>
+      <c r="G12" t="s">
         <v>85</v>
-      </c>
-      <c r="E12" t="s">
-        <v>16</v>
-      </c>
-      <c r="F12" t="s">
-        <v>77</v>
-      </c>
-      <c r="G12" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="14" spans="1:9">
       <c r="A14" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="16" spans="1:9">
       <c r="A16" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
   </sheetData>
@@ -1320,31 +1325,31 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B1" t="s">
         <v>20</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>21</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>22</v>
-      </c>
-      <c r="D1" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -1364,37 +1369,37 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B1" t="s">
         <v>27</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>28</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>29</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>30</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>31</v>
-      </c>
-      <c r="F1" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>

--- a/questions.xlsx
+++ b/questions.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kubonanako/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:20001_{4939D687-B65A-D34E-8A13-FA8B4D1B0076}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{828BD35C-E3FF-AF43-94E2-C5C2A84C6C83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="16140" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="調査概要" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,6 @@
     <sheet name="ロジック" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="0"/>
-  <fileRecoveryPr repairLoad="1"/>
 </workbook>
 </file>
 
@@ -578,10 +577,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>tezt3</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>Q12</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -591,6 +586,10 @@
   </si>
   <si>
     <t>Q2</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>text3</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1067,7 +1066,7 @@
     </row>
     <row r="2" spans="1:9">
       <c r="A2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B2" t="s">
         <v>45</v>
@@ -1087,7 +1086,7 @@
     </row>
     <row r="3" spans="1:9">
       <c r="A3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B3" t="s">
         <v>49</v>
@@ -1270,7 +1269,7 @@
         <v>83</v>
       </c>
       <c r="C12" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="E12" t="s">
         <v>15</v>
@@ -1279,7 +1278,7 @@
         <v>76</v>
       </c>
       <c r="G12" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="13" spans="1:9">

--- a/questions.xlsx
+++ b/questions.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kubonanako/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{828BD35C-E3FF-AF43-94E2-C5C2A84C6C83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8744A864-0A53-BF44-8A91-9C163443D274}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="16140" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="620" windowWidth="28800" windowHeight="16140" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="調査概要" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="87">
   <si>
     <t>項目</t>
   </si>
@@ -586,10 +586,6 @@
   </si>
   <si>
     <t>Q2</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>text3</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1269,7 +1265,7 @@
         <v>83</v>
       </c>
       <c r="C12" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="E12" t="s">
         <v>15</v>

--- a/questions.xlsx
+++ b/questions.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kubonanako/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8744A864-0A53-BF44-8A91-9C163443D274}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{856F565D-5107-4743-A7F4-EFE915AA0EE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="620" windowWidth="28800" windowHeight="16140" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="8640" yWindow="620" windowWidth="20160" windowHeight="16140" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="調査概要" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="93">
   <si>
     <t>項目</t>
   </si>
@@ -558,7 +558,19 @@
     <t>繰り返し元QID</t>
   </si>
   <si>
-    <t>糸島の「{word}」からさらに連想されることを3つ以内で回答してください。正解はありません。</t>
+    <t>Q12</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Q1</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Q2</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>糸島の「{word}」からさらに連想されることを5つ以内で回答してください。正解はありません。</t>
     <rPh sb="0" eb="2">
       <t>イトシマ</t>
     </rPh>
@@ -577,15 +589,74 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>Q12</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>Q1</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>Q2</t>
+    <t>糸島に対して、どのような気持ちを抱きますか？最大5つ選択してください。</t>
+    <rPh sb="22" eb="24">
+      <t>サイダイ</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>センタク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>あこがれる,美しい（きれい）,変化がある,多様性がある,安らぐ,親しみがある,歴史がある,明るい, 楽しい,にぎやか,活気がある,若々しい,新しい,先進的</t>
+    <rPh sb="6" eb="7">
+      <t>ウツクセィ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>ヘn</t>
+    </rPh>
+    <rPh sb="21" eb="24">
+      <t>タヨウ</t>
+    </rPh>
+    <rPh sb="28" eb="29">
+      <t>ヤスラグ</t>
+    </rPh>
+    <rPh sb="32" eb="33">
+      <t>シタシミ</t>
+    </rPh>
+    <rPh sb="39" eb="41">
+      <t>レキセィ</t>
+    </rPh>
+    <rPh sb="45" eb="46">
+      <t>アカルイ</t>
+    </rPh>
+    <rPh sb="50" eb="51">
+      <t>タノセィ</t>
+    </rPh>
+    <rPh sb="59" eb="61">
+      <t>カッキ</t>
+    </rPh>
+    <rPh sb="65" eb="66">
+      <t>ワカワカセィ</t>
+    </rPh>
+    <rPh sb="70" eb="71">
+      <t>アタラセィ</t>
+    </rPh>
+    <rPh sb="74" eb="77">
+      <t>センシn</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Q13</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>multiselect5</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>自由記述</t>
+  </si>
+  <si>
+    <t>なぜ「{word}」という気持ちを抱きましたか？</t>
+    <rPh sb="13" eb="15">
+      <t>キモティ</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>イダキ</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1027,7 +1098,7 @@
     <col min="1" max="1" width="15.33203125" customWidth="1"/>
     <col min="2" max="2" width="78.5" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="28" customWidth="1"/>
-    <col min="4" max="4" width="58.5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="128.33203125" bestFit="1" customWidth="1"/>
     <col min="5" max="9" width="28" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1062,7 +1133,7 @@
     </row>
     <row r="2" spans="1:9">
       <c r="A2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B2" t="s">
         <v>45</v>
@@ -1082,7 +1153,7 @@
     </row>
     <row r="3" spans="1:9">
       <c r="A3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B3" t="s">
         <v>49</v>
@@ -1262,7 +1333,7 @@
         <v>66</v>
       </c>
       <c r="B12" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="C12" t="s">
         <v>80</v>
@@ -1274,17 +1345,44 @@
         <v>76</v>
       </c>
       <c r="G12" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" t="s">
         <v>67</v>
       </c>
+      <c r="B13" t="s">
+        <v>87</v>
+      </c>
+      <c r="C13" t="s">
+        <v>90</v>
+      </c>
+      <c r="D13" t="s">
+        <v>88</v>
+      </c>
+      <c r="E13" t="s">
+        <v>15</v>
+      </c>
+      <c r="G13" t="s">
+        <v>89</v>
+      </c>
     </row>
     <row r="14" spans="1:9">
       <c r="A14" t="s">
         <v>68</v>
+      </c>
+      <c r="B14" t="s">
+        <v>92</v>
+      </c>
+      <c r="C14" t="s">
+        <v>91</v>
+      </c>
+      <c r="E14" t="s">
+        <v>15</v>
+      </c>
+      <c r="F14" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="15" spans="1:9">

--- a/questions.xlsx
+++ b/questions.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kubonanako/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{856F565D-5107-4743-A7F4-EFE915AA0EE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E296AF2-864D-1141-878B-B7427C5D893C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="8640" yWindow="620" windowWidth="20160" windowHeight="16140" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="96">
   <si>
     <t>項目</t>
   </si>
@@ -658,6 +658,17 @@
       <t>イダキ</t>
     </rPh>
     <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Q4</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Q3</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Q8</t>
   </si>
 </sst>
 </file>
@@ -1173,7 +1184,7 @@
     </row>
     <row r="4" spans="1:9">
       <c r="A4" t="s">
-        <v>17</v>
+        <v>94</v>
       </c>
       <c r="B4" t="s">
         <v>52</v>
@@ -1193,7 +1204,7 @@
     </row>
     <row r="5" spans="1:9">
       <c r="A5" t="s">
-        <v>18</v>
+        <v>93</v>
       </c>
       <c r="B5" t="s">
         <v>54</v>
@@ -1273,7 +1284,7 @@
     </row>
     <row r="9" spans="1:9">
       <c r="A9" t="s">
-        <v>63</v>
+        <v>95</v>
       </c>
       <c r="B9" t="s">
         <v>72</v>

--- a/questions.xlsx
+++ b/questions.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kubonanako/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E296AF2-864D-1141-878B-B7427C5D893C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B4D6675-C186-9545-B048-A1EA0CF18D0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="8640" yWindow="620" windowWidth="20160" windowHeight="16140" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="97">
   <si>
     <t>項目</t>
   </si>
@@ -306,9 +306,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>はい→Q5 / いいえ→END</t>
-  </si>
-  <si>
     <t>〇〇地域を訪問したことがありますか？</t>
     <rPh sb="0" eb="2">
       <t>〇〇</t>
@@ -669,6 +666,14 @@
   </si>
   <si>
     <t>Q8</t>
+  </si>
+  <si>
+    <t>END</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>はい→Q5 / いいえ→END</t>
+    <phoneticPr fontId="1"/>
   </si>
 </sst>
 </file>
@@ -1121,7 +1126,7 @@
         <v>9</v>
       </c>
       <c r="C1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D1" t="s">
         <v>10</v>
@@ -1130,7 +1135,7 @@
         <v>11</v>
       </c>
       <c r="F1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G1" t="s">
         <v>12</v>
@@ -1144,7 +1149,7 @@
     </row>
     <row r="2" spans="1:9">
       <c r="A2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B2" t="s">
         <v>45</v>
@@ -1164,7 +1169,7 @@
     </row>
     <row r="3" spans="1:9">
       <c r="A3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B3" t="s">
         <v>49</v>
@@ -1184,7 +1189,7 @@
     </row>
     <row r="4" spans="1:9">
       <c r="A4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B4" t="s">
         <v>52</v>
@@ -1204,7 +1209,7 @@
     </row>
     <row r="5" spans="1:9">
       <c r="A5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B5" t="s">
         <v>54</v>
@@ -1219,7 +1224,7 @@
         <v>15</v>
       </c>
       <c r="H5" t="s">
-        <v>55</v>
+        <v>96</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -1227,7 +1232,7 @@
         <v>42</v>
       </c>
       <c r="B6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C6" t="s">
         <v>46</v>
@@ -1239,7 +1244,7 @@
         <v>15</v>
       </c>
       <c r="H6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -1247,19 +1252,19 @@
         <v>43</v>
       </c>
       <c r="B7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C7" t="s">
         <v>46</v>
       </c>
       <c r="D7" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E7" t="s">
         <v>15</v>
       </c>
       <c r="G7" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -1267,27 +1272,27 @@
         <v>44</v>
       </c>
       <c r="B8" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C8" t="s">
+        <v>58</v>
+      </c>
+      <c r="D8" t="s">
         <v>59</v>
-      </c>
-      <c r="D8" t="s">
-        <v>60</v>
       </c>
       <c r="E8" t="s">
         <v>15</v>
       </c>
       <c r="G8" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B9" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C9" t="s">
         <v>46</v>
@@ -1299,116 +1304,119 @@
         <v>15</v>
       </c>
       <c r="H9" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B10" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C10" t="s">
         <v>46</v>
       </c>
       <c r="D10" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E10" t="s">
         <v>15</v>
       </c>
       <c r="G10" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B11" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C11" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E11" t="s">
         <v>15</v>
       </c>
       <c r="G11" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B12" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C12" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E12" t="s">
         <v>15</v>
       </c>
       <c r="F12" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G12" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B13" t="s">
+        <v>86</v>
+      </c>
+      <c r="C13" t="s">
+        <v>89</v>
+      </c>
+      <c r="D13" t="s">
         <v>87</v>
-      </c>
-      <c r="C13" t="s">
-        <v>90</v>
-      </c>
-      <c r="D13" t="s">
-        <v>88</v>
       </c>
       <c r="E13" t="s">
         <v>15</v>
       </c>
       <c r="G13" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="14" spans="1:9">
       <c r="A14" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B14" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C14" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E14" t="s">
         <v>15</v>
       </c>
       <c r="F14" t="s">
-        <v>83</v>
+        <v>82</v>
+      </c>
+      <c r="G14" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="16" spans="1:9">
       <c r="A16" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
   </sheetData>

--- a/questions.xlsx
+++ b/questions.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kubonanako/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B4D6675-C186-9545-B048-A1EA0CF18D0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26A96A8F-58C3-4E48-BAFC-43842D48C8C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8640" yWindow="620" windowWidth="20160" windowHeight="16140" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="調査概要" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="97">
   <si>
     <t>項目</t>
   </si>
@@ -1223,6 +1223,9 @@
       <c r="E5" t="s">
         <v>15</v>
       </c>
+      <c r="G5" t="s">
+        <v>96</v>
+      </c>
       <c r="H5" t="s">
         <v>96</v>
       </c>
@@ -1243,6 +1246,9 @@
       <c r="E6" t="s">
         <v>15</v>
       </c>
+      <c r="G6" t="s">
+        <v>56</v>
+      </c>
       <c r="H6" t="s">
         <v>56</v>
       </c>
@@ -1302,6 +1308,9 @@
       </c>
       <c r="E9" t="s">
         <v>15</v>
+      </c>
+      <c r="G9" t="s">
+        <v>72</v>
       </c>
       <c r="H9" t="s">
         <v>72</v>

--- a/questions.xlsx
+++ b/questions.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kubonanako/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26A96A8F-58C3-4E48-BAFC-43842D48C8C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{382B27BA-99BD-8442-A864-30DEC1A4C808}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="12460" yWindow="620" windowWidth="16340" windowHeight="16140" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="調査概要" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="95">
   <si>
     <t>項目</t>
   </si>
@@ -52,25 +52,7 @@
     <t>QID</t>
   </si>
   <si>
-    <t>設問文</t>
-  </si>
-  <si>
-    <t>選択肢（カンマ区切り）</t>
-  </si>
-  <si>
-    <t>必須（YES/NO）</t>
-  </si>
-  <si>
-    <t>次の設問（通常）</t>
-  </si>
-  <si>
-    <t>次の設問（条件分岐）</t>
-  </si>
-  <si>
     <t>備考</t>
-  </si>
-  <si>
-    <t>YES</t>
   </si>
   <si>
     <t>Q2</t>
@@ -319,10 +301,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>はい→Q6 / いいえ→Q7</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>過去3年間に何度〇〇地域を訪問しましたか？</t>
     <rPh sb="0" eb="2">
       <t>カコ</t>
@@ -432,10 +410,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>はい→Q9 / いいえ→END</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>ここ3年で〇〇地域の食品や飲料を購入した回数を選択肢してください。</t>
     <rPh sb="3" eb="4">
       <t>ネn</t>
@@ -540,19 +514,12 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>回答形式（単一選択 / 複数選択 / 自由記述 / 数値）</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>text5</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>Q11</t>
     <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>繰り返し元QID</t>
   </si>
   <si>
     <t>Q12</t>
@@ -665,6 +632,10 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
+    <t>Q6</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
     <t>Q8</t>
   </si>
   <si>
@@ -672,15 +643,40 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>はい→Q5 / いいえ→END</t>
-    <phoneticPr fontId="1"/>
+    <t>options</t>
+  </si>
+  <si>
+    <t>branch_はい</t>
+  </si>
+  <si>
+    <t>text</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>type</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>next</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>branch_いいえ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Q9</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>repeat_source</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -696,6 +692,15 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="2"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -724,11 +729,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -1043,7 +1049,7 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -1051,7 +1057,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -1059,7 +1065,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -1067,7 +1073,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -1081,7 +1087,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -1089,7 +1095,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -1097,7 +1103,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -1115,317 +1121,272 @@
     <col min="2" max="2" width="78.5" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="28" customWidth="1"/>
     <col min="4" max="4" width="128.33203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="9" width="28" customWidth="1"/>
+    <col min="5" max="8" width="28" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
-      <c r="A1" t="s">
+      <c r="A1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="E1" t="s">
+        <v>94</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="I1" t="s">
         <v>9</v>
-      </c>
-      <c r="C1" t="s">
-        <v>78</v>
-      </c>
-      <c r="D1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F1" t="s">
-        <v>81</v>
-      </c>
-      <c r="G1" t="s">
-        <v>12</v>
-      </c>
-      <c r="H1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I1" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" t="s">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="B2" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="C2" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="D2" t="s">
-        <v>48</v>
-      </c>
-      <c r="E2" t="s">
-        <v>15</v>
-      </c>
-      <c r="G2" t="s">
-        <v>16</v>
+        <v>42</v>
+      </c>
+      <c r="F2" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="B3" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="C3" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="D3" t="s">
-        <v>50</v>
-      </c>
-      <c r="E3" t="s">
-        <v>15</v>
-      </c>
-      <c r="G3" t="s">
-        <v>17</v>
+        <v>44</v>
+      </c>
+      <c r="F3" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" t="s">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="B4" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="C4" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="D4" t="s">
-        <v>51</v>
-      </c>
-      <c r="E4" t="s">
-        <v>15</v>
-      </c>
-      <c r="G4" t="s">
-        <v>18</v>
+        <v>45</v>
+      </c>
+      <c r="F4" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="B5" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="C5" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="D5" t="s">
-        <v>53</v>
-      </c>
-      <c r="E5" t="s">
-        <v>15</v>
+        <v>47</v>
       </c>
       <c r="G5" t="s">
-        <v>96</v>
+        <v>36</v>
       </c>
       <c r="H5" t="s">
-        <v>96</v>
+        <v>86</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="B6" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="C6" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="D6" t="s">
-        <v>53</v>
-      </c>
-      <c r="E6" t="s">
-        <v>15</v>
+        <v>47</v>
       </c>
       <c r="G6" t="s">
-        <v>56</v>
-      </c>
-      <c r="H6" t="s">
-        <v>56</v>
+        <v>84</v>
       </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="B7" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="C7" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="D7" t="s">
-        <v>74</v>
-      </c>
-      <c r="E7" t="s">
-        <v>15</v>
-      </c>
-      <c r="G7" t="s">
-        <v>61</v>
+        <v>66</v>
+      </c>
+      <c r="F7" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="B8" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="C8" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="D8" t="s">
-        <v>59</v>
-      </c>
-      <c r="E8" t="s">
-        <v>15</v>
-      </c>
-      <c r="G8" t="s">
-        <v>62</v>
+        <v>52</v>
+      </c>
+      <c r="F8" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="B9" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="C9" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="D9" t="s">
-        <v>53</v>
-      </c>
-      <c r="E9" t="s">
-        <v>15</v>
+        <v>47</v>
       </c>
       <c r="G9" t="s">
-        <v>72</v>
+        <v>93</v>
       </c>
       <c r="H9" t="s">
-        <v>72</v>
+        <v>86</v>
       </c>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="B10" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="C10" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="D10" t="s">
-        <v>76</v>
-      </c>
-      <c r="E10" t="s">
-        <v>15</v>
-      </c>
-      <c r="G10" t="s">
-        <v>75</v>
+        <v>68</v>
+      </c>
+      <c r="F10" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="B11" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="C11" t="s">
-        <v>79</v>
-      </c>
-      <c r="E11" t="s">
-        <v>15</v>
-      </c>
-      <c r="G11" t="s">
-        <v>80</v>
+        <v>70</v>
+      </c>
+      <c r="F11" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="B12" t="s">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="C12" t="s">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="E12" t="s">
-        <v>15</v>
+        <v>67</v>
       </c>
       <c r="F12" t="s">
-        <v>75</v>
-      </c>
-      <c r="G12" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="B13" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="C13" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="D13" t="s">
-        <v>87</v>
-      </c>
-      <c r="E13" t="s">
-        <v>15</v>
-      </c>
-      <c r="G13" t="s">
-        <v>88</v>
+        <v>77</v>
+      </c>
+      <c r="F13" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="14" spans="1:9">
       <c r="A14" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="B14" t="s">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="C14" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="E14" t="s">
-        <v>15</v>
-      </c>
-      <c r="F14" t="s">
-        <v>82</v>
-      </c>
-      <c r="G14" t="s">
-        <v>95</v>
+        <v>72</v>
       </c>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
     </row>
     <row r="16" spans="1:9">
       <c r="A16" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
     </row>
   </sheetData>
@@ -1446,31 +1407,31 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="B1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="C1" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="D1" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -1490,37 +1451,37 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="B1" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="C1" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="D1" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="E1" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="F1" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>

--- a/questions.xlsx
+++ b/questions.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kubonanako/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{382B27BA-99BD-8442-A864-30DEC1A4C808}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34F7D3E0-1E92-8D41-94F7-481D3A3D2C43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12460" yWindow="620" windowWidth="16340" windowHeight="16140" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="13680" yWindow="600" windowWidth="16340" windowHeight="16140" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="調査概要" sheetId="1" r:id="rId1"/>
@@ -643,26 +643,22 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
+    <t>type</t>
+  </si>
+  <si>
+    <t>text</t>
+  </si>
+  <si>
     <t>options</t>
   </si>
   <si>
+    <t>next</t>
+  </si>
+  <si>
     <t>branch_はい</t>
   </si>
   <si>
-    <t>text</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>type</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>next</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>branch_いいえ</t>
-    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>Q9</t>
@@ -676,7 +672,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -692,15 +688,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <family val="2"/>
-      <charset val="128"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -729,12 +716,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -1125,28 +1111,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
-      <c r="A1" s="2" t="s">
+      <c r="A1" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" t="s">
+        <v>88</v>
+      </c>
+      <c r="C1" t="s">
+        <v>87</v>
+      </c>
+      <c r="D1" t="s">
         <v>89</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>87</v>
       </c>
       <c r="E1" t="s">
         <v>94</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" t="s">
+        <v>90</v>
+      </c>
+      <c r="G1" t="s">
         <v>91</v>
       </c>
-      <c r="G1" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" t="s">
         <v>92</v>
       </c>
       <c r="I1" t="s">

--- a/questions.xlsx
+++ b/questions.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kubonanako/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34F7D3E0-1E92-8D41-94F7-481D3A3D2C43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1830FD7F-5BD5-004C-B42F-AC6B1F0104C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13680" yWindow="600" windowWidth="16340" windowHeight="16140" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="調査概要" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="92">
   <si>
     <t>項目</t>
   </si>
@@ -377,15 +377,6 @@
   </si>
   <si>
     <t>Q13</t>
-  </si>
-  <si>
-    <t>Q14</t>
-  </si>
-  <si>
-    <t>Q15</t>
-  </si>
-  <si>
-    <t>Q16</t>
   </si>
   <si>
     <t>〇〇地域の食品や飲料を購入したことがありますか？（購入場所はどこでも可）</t>
@@ -1100,7 +1091,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:I17"/>
+  <dimension ref="A1:I14"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="15.33203125" customWidth="1"/>
@@ -1115,25 +1106,25 @@
         <v>8</v>
       </c>
       <c r="B1" t="s">
+        <v>85</v>
+      </c>
+      <c r="C1" t="s">
+        <v>84</v>
+      </c>
+      <c r="D1" t="s">
+        <v>86</v>
+      </c>
+      <c r="E1" t="s">
+        <v>91</v>
+      </c>
+      <c r="F1" t="s">
+        <v>87</v>
+      </c>
+      <c r="G1" t="s">
         <v>88</v>
       </c>
-      <c r="C1" t="s">
-        <v>87</v>
-      </c>
-      <c r="D1" t="s">
+      <c r="H1" t="s">
         <v>89</v>
-      </c>
-      <c r="E1" t="s">
-        <v>94</v>
-      </c>
-      <c r="F1" t="s">
-        <v>90</v>
-      </c>
-      <c r="G1" t="s">
-        <v>91</v>
-      </c>
-      <c r="H1" t="s">
-        <v>92</v>
       </c>
       <c r="I1" t="s">
         <v>9</v>
@@ -1141,7 +1132,7 @@
     </row>
     <row r="2" spans="1:9">
       <c r="A2" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="B2" t="s">
         <v>39</v>
@@ -1158,7 +1149,7 @@
     </row>
     <row r="3" spans="1:9">
       <c r="A3" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B3" t="s">
         <v>43</v>
@@ -1175,7 +1166,7 @@
     </row>
     <row r="4" spans="1:9">
       <c r="A4" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="B4" t="s">
         <v>46</v>
@@ -1192,7 +1183,7 @@
     </row>
     <row r="5" spans="1:9">
       <c r="A5" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="B5" t="s">
         <v>48</v>
@@ -1207,7 +1198,7 @@
         <v>36</v>
       </c>
       <c r="H5" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -1224,7 +1215,7 @@
         <v>47</v>
       </c>
       <c r="G6" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -1238,7 +1229,7 @@
         <v>40</v>
       </c>
       <c r="D7" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="F7" t="s">
         <v>54</v>
@@ -1263,10 +1254,10 @@
     </row>
     <row r="9" spans="1:9">
       <c r="A9" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="B9" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="C9" t="s">
         <v>40</v>
@@ -1275,10 +1266,10 @@
         <v>47</v>
       </c>
       <c r="G9" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="H9" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -1286,16 +1277,16 @@
         <v>56</v>
       </c>
       <c r="B10" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="C10" t="s">
         <v>40</v>
       </c>
       <c r="D10" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="F10" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -1303,13 +1294,13 @@
         <v>57</v>
       </c>
       <c r="B11" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="C11" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="F11" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
     </row>
     <row r="12" spans="1:9">
@@ -1317,16 +1308,16 @@
         <v>58</v>
       </c>
       <c r="B12" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="C12" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="E12" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="F12" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
     </row>
     <row r="13" spans="1:9">
@@ -1334,16 +1325,16 @@
         <v>59</v>
       </c>
       <c r="B13" t="s">
+        <v>73</v>
+      </c>
+      <c r="C13" t="s">
         <v>76</v>
       </c>
-      <c r="C13" t="s">
-        <v>79</v>
-      </c>
       <c r="D13" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="F13" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
     </row>
     <row r="14" spans="1:9">
@@ -1351,28 +1342,13 @@
         <v>60</v>
       </c>
       <c r="B14" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="C14" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="E14" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9">
-      <c r="A15" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9">
-      <c r="A16" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1">
-      <c r="A17" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
     </row>
   </sheetData>

--- a/questions.xlsx
+++ b/questions.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kubonanako/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1830FD7F-5BD5-004C-B42F-AC6B1F0104C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64AB5EA7-970C-5440-A6D5-7A3FE5B1F20E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/questions.xlsx
+++ b/questions.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kubonanako/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64AB5EA7-970C-5440-A6D5-7A3FE5B1F20E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8869EEF4-0219-5C49-B29D-49999CAB3DC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/questions.xlsx
+++ b/questions.xlsx
@@ -8,13 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kubonanako/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8869EEF4-0219-5C49-B29D-49999CAB3DC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07EE7E82-56DC-3843-8815-CDEC3DA246C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="12460" yWindow="600" windowWidth="16340" windowHeight="16140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="調査概要" sheetId="1" r:id="rId1"/>
-    <sheet name="設問一覧" sheetId="2" r:id="rId2"/>
+    <sheet name="設問一覧" sheetId="2" r:id="rId1"/>
+    <sheet name="調査概要" sheetId="1" r:id="rId2"/>
     <sheet name="選択肢マスタ" sheetId="3" r:id="rId3"/>
     <sheet name="ロジック" sheetId="4" r:id="rId4"/>
   </sheets>
@@ -1013,83 +1013,6 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B8"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
-  <cols>
-    <col min="1" max="1" width="25" customWidth="1"/>
-    <col min="2" max="2" width="71.1640625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2">
-      <c r="A5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B5" s="1"/>
-    </row>
-    <row r="6" spans="1:2">
-      <c r="A6" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2">
-      <c r="A7" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2">
-      <c r="A8" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>35</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:I14"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
@@ -1349,6 +1272,83 @@
       </c>
       <c r="E14" t="s">
         <v>69</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:B8"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
+  <cols>
+    <col min="1" max="1" width="25" customWidth="1"/>
+    <col min="2" max="2" width="71.1640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1"/>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>35</v>
       </c>
     </row>
   </sheetData>

--- a/questions.xlsx
+++ b/questions.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kubonanako/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07EE7E82-56DC-3843-8815-CDEC3DA246C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0DC3FCC-448D-954B-B884-034CCFA200EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12460" yWindow="600" windowWidth="16340" windowHeight="16140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="設問一覧" sheetId="2" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="91">
   <si>
     <t>項目</t>
   </si>
@@ -181,19 +181,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>単一選択</t>
-  </si>
-  <si>
-    <t>単一選択</t>
-    <rPh sb="0" eb="2">
-      <t>タンイ</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>センタク</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>19歳以下,20〜29歳,30〜39歳,40〜49歳,50〜59歳,60〜69歳,70歳以上</t>
     <rPh sb="2" eb="3">
       <t>サイ</t>
@@ -317,16 +304,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>複数選択</t>
-    <rPh sb="0" eb="2">
-      <t>フクスウ</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>センタク</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>電車,バス,車,バイク,自転車,その他</t>
     <rPh sb="0" eb="2">
       <t>デンセィア</t>
@@ -602,9 +579,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>自由記述</t>
-  </si>
-  <si>
     <t>なぜ「{word}」という気持ちを抱きましたか？</t>
     <rPh sb="13" eb="15">
       <t>キモティ</t>
@@ -649,6 +623,10 @@
     <t>branch_はい</t>
   </si>
   <si>
+    <t>text</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
     <t>branch_いいえ</t>
   </si>
   <si>
@@ -657,6 +635,13 @@
   </si>
   <si>
     <t>repeat_source</t>
+  </si>
+  <si>
+    <t>radio</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>multiselect</t>
   </si>
 </sst>
 </file>
@@ -1029,25 +1014,25 @@
         <v>8</v>
       </c>
       <c r="B1" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="C1" t="s">
+        <v>80</v>
+      </c>
+      <c r="D1" t="s">
+        <v>82</v>
+      </c>
+      <c r="E1" t="s">
+        <v>88</v>
+      </c>
+      <c r="F1" t="s">
+        <v>83</v>
+      </c>
+      <c r="G1" t="s">
         <v>84</v>
       </c>
-      <c r="D1" t="s">
+      <c r="H1" t="s">
         <v>86</v>
-      </c>
-      <c r="E1" t="s">
-        <v>91</v>
-      </c>
-      <c r="F1" t="s">
-        <v>87</v>
-      </c>
-      <c r="G1" t="s">
-        <v>88</v>
-      </c>
-      <c r="H1" t="s">
-        <v>89</v>
       </c>
       <c r="I1" t="s">
         <v>9</v>
@@ -1055,16 +1040,16 @@
     </row>
     <row r="2" spans="1:9">
       <c r="A2" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="B2" t="s">
         <v>39</v>
       </c>
       <c r="C2" t="s">
-        <v>41</v>
+        <v>89</v>
       </c>
       <c r="D2" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F2" t="s">
         <v>10</v>
@@ -1072,16 +1057,16 @@
     </row>
     <row r="3" spans="1:9">
       <c r="A3" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="B3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C3" t="s">
-        <v>41</v>
+        <v>89</v>
       </c>
       <c r="D3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F3" t="s">
         <v>11</v>
@@ -1089,16 +1074,16 @@
     </row>
     <row r="4" spans="1:9">
       <c r="A4" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="B4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C4" t="s">
-        <v>40</v>
+        <v>89</v>
       </c>
       <c r="D4" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F4" t="s">
         <v>12</v>
@@ -1106,22 +1091,22 @@
     </row>
     <row r="5" spans="1:9">
       <c r="A5" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="B5" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C5" t="s">
-        <v>40</v>
+        <v>89</v>
       </c>
       <c r="D5" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="G5" t="s">
         <v>36</v>
       </c>
       <c r="H5" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -1129,16 +1114,16 @@
         <v>36</v>
       </c>
       <c r="B6" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C6" t="s">
-        <v>40</v>
+        <v>89</v>
       </c>
       <c r="D6" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="G6" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -1146,16 +1131,16 @@
         <v>37</v>
       </c>
       <c r="B7" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C7" t="s">
-        <v>40</v>
+        <v>89</v>
       </c>
       <c r="D7" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="F7" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -1163,115 +1148,115 @@
         <v>38</v>
       </c>
       <c r="B8" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="C8" t="s">
-        <v>51</v>
+        <v>90</v>
       </c>
       <c r="D8" t="s">
+        <v>49</v>
+      </c>
+      <c r="F8" t="s">
         <v>52</v>
-      </c>
-      <c r="F8" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="B9" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="C9" t="s">
-        <v>40</v>
+        <v>89</v>
       </c>
       <c r="D9" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="G9" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="H9" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="B10" t="s">
+        <v>59</v>
+      </c>
+      <c r="C10" t="s">
+        <v>89</v>
+      </c>
+      <c r="D10" t="s">
         <v>62</v>
       </c>
-      <c r="C10" t="s">
-        <v>40</v>
-      </c>
-      <c r="D10" t="s">
-        <v>65</v>
-      </c>
       <c r="F10" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="B11" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="C11" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="F11" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="B12" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="C12" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="E12" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="F12" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="B13" t="s">
+        <v>70</v>
+      </c>
+      <c r="C13" t="s">
         <v>73</v>
       </c>
-      <c r="C13" t="s">
-        <v>76</v>
-      </c>
       <c r="D13" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="F13" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
     </row>
     <row r="14" spans="1:9">
       <c r="A14" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="B14" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="C14" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="E14" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
     </row>
   </sheetData>
